--- a/tasks/finalpool/canvas-enrollment-forecast-excel-gform-email/groundtruth_workspace/Enrollment_Analysis.xlsx
+++ b/tasks/finalpool/canvas-enrollment-forecast-excel-gform-email/groundtruth_workspace/Enrollment_Analysis.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -466,16 +466,6 @@
           <t>Student_Count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Teacher_Count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TA_Count</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -494,12 +484,6 @@
       <c r="D2" t="n">
         <v>383</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,12 +502,6 @@
       <c r="D3" t="n">
         <v>365</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,12 +520,6 @@
       <c r="D4" t="n">
         <v>1767</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,12 +538,6 @@
       <c r="D5" t="n">
         <v>2237</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,12 +556,6 @@
       <c r="D6" t="n">
         <v>1613</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,12 +574,6 @@
       <c r="D7" t="n">
         <v>2292</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -638,12 +592,6 @@
       <c r="D8" t="n">
         <v>1936</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -662,12 +610,6 @@
       <c r="D9" t="n">
         <v>2498</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -686,12 +628,6 @@
       <c r="D10" t="n">
         <v>1303</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -710,12 +646,6 @@
       <c r="D11" t="n">
         <v>1938</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -734,12 +664,6 @@
       <c r="D12" t="n">
         <v>1228</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -758,12 +682,6 @@
       <c r="D13" t="n">
         <v>1803</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -782,12 +700,6 @@
       <c r="D14" t="n">
         <v>1052</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -806,12 +718,6 @@
       <c r="D15" t="n">
         <v>694</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -830,12 +736,6 @@
       <c r="D16" t="n">
         <v>1188</v>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -854,12 +754,6 @@
       <c r="D17" t="n">
         <v>1614</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -878,12 +772,6 @@
       <c r="D18" t="n">
         <v>2283</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -902,12 +790,6 @@
       <c r="D19" t="n">
         <v>1500</v>
       </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -926,12 +808,6 @@
       <c r="D20" t="n">
         <v>2365</v>
       </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -950,12 +826,6 @@
       <c r="D21" t="n">
         <v>952</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -974,12 +844,6 @@
       <c r="D22" t="n">
         <v>833</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -997,12 +861,6 @@
       </c>
       <c r="D23" t="n">
         <v>749</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
